--- a/Syllabus.xlsx
+++ b/Syllabus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/csartori/GitHub/Informatics-Stats-and-Maths/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2B9F0A-E430-F741-879A-9679987443B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3162EB08-E937-9A4A-AF90-64E785CF3FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="600" windowWidth="32960" windowHeight="21960" xr2:uid="{FF500EC8-34E6-D84A-8C22-9C1910F4A916}"/>
+    <workbookView xWindow="1560" yWindow="600" windowWidth="37160" windowHeight="21960" xr2:uid="{FF500EC8-34E6-D84A-8C22-9C1910F4A916}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,193 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="43">
+  <si>
+    <t>Hour</t>
+  </si>
+  <si>
+    <t>Topics</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>General description of the course, assessment method. 
+Defining IT, a short history.</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking: lan, wan, network types, dns, url. Digital representation of information. Numbers, characters. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integer and non-integer numbers: the binary representation; the mantissa/exponent representation and the floating point. Differences between real numbers and floating point: precision and approximation, arithmetic properties. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Operation principles. Software and software layers. Instruction execution engine: the fetch/execute cycle and the clock. Architecture of a computer: the Von Neuman model. 
+Memories. Input/output devices. CPU types.
+Operating system. Bootstrap process. Multitasking. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algorithmic thinking: the five properties of an algorithm. Programming languages and life cycle of a program. Examples of algorithms: the example of compound interest. </t>
+  </si>
+  <si>
+    <t>The Interactive Development Environment RStudio. Creating, editing and running an R program. Usage of the working windows, help system. Examples. 
+R - interactive and batch usage. The R  System Environment and the memory. Expressions and assignments. Operand Types. Operator types and priorities. Examples of expressions.
+Logical operators and De Morgan laws.
+Changing the type of an expression. Console input and output. Input from file. Writing loops. For and while constructs. 
+Compound interest in R. Integer division in R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repetition with for, sequences. Translation of the example of the compound interest into an R program. Discussion on the valid input ranges. Repetition based on condition. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example of exponential with McLaurin Formula. Conditional instructions. Nested conditional instructions, usage of braces. Sequences of instructions and blocks. Programming repetitions with the repeat construct. </t>
+  </si>
+  <si>
+    <t>Examples of translation of algorithms in R: the computation of the exponential with the MacLaurin series. Conditional execution: the if construct. Chain of conditionals. From algorithm to R program</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Lab 2 Count NA, Dot prod, Harmonic mean (non sviluppato)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectors and computations with vectors. Storing values in vectors, using values of vector elements. Looking for a value in a vector. More on vector index expression, selection of vector elements based on condition. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abstractions and functions. Function version of the MacLaurin example. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lists: creation and usage. Example of function returning a list. Exercise: the Gini concentration index. Matrices in R. Examples. Example of matrix multiplication.  Arrays. Vectors, matrices, arrays: equivalence with mathematical objects. Examples with vectors and matrices.  Implementing set operations on sets represented as vectors: subset test, unique, union, intersection, difference. </t>
+  </si>
+  <si>
+    <t>Lab 3 - Count inversions, Count values between, Max increment position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini Concentration Index.
+Data frames and motivations for their usage. Creating and using data frames. Input from file and data frame creation. Scan and read.csv. </t>
+  </si>
+  <si>
+    <t>Accessing and reshaping a data frame.</t>
+  </si>
+  <si>
+    <t>Review of first part</t>
+  </si>
+  <si>
+    <t>Lab 4 - Polynomial in x, using power, Polynomial in x using Horner</t>
+  </si>
+  <si>
+    <t>Lab 5 - Counting frequencies of modalities from csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algorithms: sort. From algorithm to the R program. The bubble sort algorithm. 
+Recursive functions. Recursive vs iterative. Examples: Factorial, Fibonacci, Merge_Sort implementation and intuition on computational complexity. </t>
+  </si>
+  <si>
+    <t>Determinant of square matrix with Laplace formula. Examples with the matrix algebra. The echelon form: checking the condition. The elementary row operations. Echelon reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing the determinant of a square matrix: the Laplace formula vs the echelon reduction: intuition on comparison of the computational complexities. </t>
+  </si>
+  <si>
+    <t>Lab 6 - Quantiles from data frame read from csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduction to computational complexity. Comparing the effort of different procedures that obtain the same result. Time complexity. Evaluation and comparison of complexities; asymptotic complexity. </t>
+  </si>
+  <si>
+    <t>The "big O" notation. Comparing linear search and binary search. Examples of general algorithms and their computational complexity. The knapsack problem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Searching a sorted list: the binary search. Binary search. String manipulation with R. Example of summarisation of a data frame according to a categorical column. </t>
+  </si>
+  <si>
+    <t>Lab 7 - Rectangles membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectorization in R: implicit vectorization and vectorized functions. Comparisons of efficiency. The apply family of functions for the intrinsic vectorization. Subsetting data structures in R. Types of subsetting. Types of indexing. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strings and string functions. Regular expressions for string manipulation.
+Plotting data.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Lehmer generator. Generation of random numbers in R. Repetition of a random sequence by means of the seed. Types of generation: continuous uniform, discrete uniform, discrete with assigned probability. </t>
+  </si>
+  <si>
+    <t>Lab 8 - Analysis of string lenghts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montecarlo methods. Computing Pi with Montecarlo method. Numerical methods. Minimum of a function with the golden section. Zeroes of a function with the Newton method. Zeroes of a function with the bisection method. </t>
+  </si>
+  <si>
+    <t>Numerical methods - continued</t>
+  </si>
+  <si>
+    <t>Longitudinal data https://www.statmethods.net/input/dates.html</t>
+  </si>
+  <si>
+    <t>Lab 9 - Classification of numeric values in ranges</t>
+  </si>
+  <si>
+    <t>Exercises on writing algorithms and translating algorithms to R: sequence analysis 1. Exercises on writing algorithms and translating algorithms to R: sequence analysis 3</t>
+  </si>
+  <si>
+    <t>Lab 10 - Mock lab exam</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -51,11 +232,14 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="16"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,7 +250,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -74,23 +258,108 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -120,13 +389,15 @@
       <sheetName val="Foglio2"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
+      <sheetData sheetId="0">
         <row r="1">
           <cell r="A1" t="str">
             <v>Date</v>
           </cell>
           <cell r="B1" t="str">
+            <v>Hour</v>
+          </cell>
+          <cell r="D1" t="str">
             <v>Topics</v>
           </cell>
         </row>
@@ -135,9 +406,14 @@
             <v>46062</v>
           </cell>
           <cell r="B2" t="str">
-            <v xml:space="preserve">General description of the course, assessment method. 
-Defining IT, a short history.
-Networking: lan, wan, network types, dns, url. </v>
+            <v>9</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>General description of the course, assessment method. 
+Defining IT, a short history.</v>
           </cell>
         </row>
         <row r="3">
@@ -145,34 +421,57 @@
             <v>46063</v>
           </cell>
           <cell r="B3" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v xml:space="preserve">Networking: lan, wan, network types, dns, url. Digital representation of information. Numbers, characters. </v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>46064</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v xml:space="preserve">Integer and non-integer numbers: the binary representation; the mantissa/exponent representation and the floating point. Differences between real numbers and floating point: precision and approximation, arithmetic properties. </v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>46069</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D5" t="str">
             <v xml:space="preserve">Computer Operation principles. Software and software layers. Instruction execution engine: the fetch/execute cycle and the clock. Architecture of a computer: the Von Neuman model. 
 Memories. Input/output devices. CPU types.
 Operating system. Bootstrap process. Multitasking. </v>
           </cell>
         </row>
-        <row r="4">
-          <cell r="A4">
-            <v>46064</v>
-          </cell>
-          <cell r="B4" t="str">
-            <v xml:space="preserve">Digital representation of information. Numbers, characters. Integer and non-integer numbers: the binary representation; the mantissa/exponent representation and the floating point. Differences between real numbers and floating point: precision and approximation, arithmetic properties. </v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>46069</v>
-          </cell>
-          <cell r="B5" t="str">
-            <v>Algorithmic thinking: the five properties of an algorithm. Programming languages and life cycle of a program. Examples of algorithms: the example of compound interest.</v>
-          </cell>
-        </row>
         <row r="6">
           <cell r="A6">
             <v>46070</v>
           </cell>
           <cell r="B6" t="str">
-            <v>Writing loops. For and while constructs. 
-Compound interest in R. Integer division in R</v>
+            <v>11</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v xml:space="preserve">Algorithmic thinking: the five properties of an algorithm. Programming languages and life cycle of a program. Examples of algorithms: the example of compound interest. </v>
           </cell>
         </row>
         <row r="7">
@@ -180,10 +479,17 @@
             <v>46071</v>
           </cell>
           <cell r="B7" t="str">
-            <v xml:space="preserve">The Interactive Development Environment RStudio. Creating, editing and running an R program. Usage of the working windows, help system. Examples. 
+            <v>11</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>The Interactive Development Environment RStudio. Creating, editing and running an R program. Usage of the working windows, help system. Examples. 
 R - interactive and batch usage. The R  System Environment and the memory. Expressions and assignments. Operand Types. Operator types and priorities. Examples of expressions.
 Logical operators and De Morgan laws.
-Changing the type of an expression. Console input and output. Input from file. </v>
+Changing the type of an expression. Console input and output. Input from file. Writing loops. For and while constructs. 
+Compound interest in R. Integer division in R</v>
           </cell>
         </row>
         <row r="8">
@@ -191,6 +497,12 @@
             <v>46076</v>
           </cell>
           <cell r="B8" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D8" t="str">
             <v xml:space="preserve">Repetition with for, sequences. Translation of the example of the compound interest into an R program. Discussion on the valid input ranges. Repetition based on condition. </v>
           </cell>
         </row>
@@ -199,6 +511,12 @@
             <v>46077</v>
           </cell>
           <cell r="B9" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D9" t="str">
             <v xml:space="preserve">Example of exponential with McLaurin Formula. Conditional instructions. Nested conditional instructions, usage of braces. Sequences of instructions and blocks. Programming repetitions with the repeat construct. </v>
           </cell>
         </row>
@@ -207,192 +525,499 @@
             <v>46078</v>
           </cell>
           <cell r="B10" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D10" t="str">
             <v>Examples of translation of algorithms in R: the computation of the exponential with the MacLaurin series. Conditional execution: the if construct. Chain of conditionals. From algorithm to R program</v>
           </cell>
         </row>
         <row r="11">
           <cell r="A11">
-            <v>46083</v>
+            <v>46079</v>
           </cell>
           <cell r="B11" t="str">
-            <v xml:space="preserve">Vectors and computations with vectors. Storing values in vectors, using values of vector elements. Looking for a value in a vector. More on vector index expression, selection of vector elements based on condition. </v>
+            <v>14</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>Lab 2 Count NA, Dot prod, Harmonic mean (non sviluppato)</v>
           </cell>
         </row>
         <row r="12">
           <cell r="A12">
-            <v>46084</v>
+            <v>46083</v>
           </cell>
           <cell r="B12" t="str">
-            <v xml:space="preserve">Abstractions and functions. Function version of the MacLaurin example. </v>
+            <v>9</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v xml:space="preserve">Vectors and computations with vectors. Storing values in vectors, using values of vector elements. Looking for a value in a vector. More on vector index expression, selection of vector elements based on condition. </v>
           </cell>
         </row>
         <row r="13">
           <cell r="A13">
-            <v>46085</v>
+            <v>46084</v>
           </cell>
           <cell r="B13" t="str">
-            <v xml:space="preserve">Lists: creation and usage. Example of function returning a list. Exercise: the Gini concentration index. Matrices in R. Examples. Example of matrix multiplication.  Arrays. Vectors, matrices, arrays: equivalence with mathematical objects. Examples with vectors and matrices.  Implementing set operations on sets represented as vectors: subset test, unique, union, intersection, difference. </v>
+            <v>11</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v xml:space="preserve">Abstractions and functions. Function version of the MacLaurin example. </v>
           </cell>
         </row>
         <row r="14">
           <cell r="A14">
+            <v>46085</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v xml:space="preserve">Lists: creation and usage. Example of function returning a list. Exercise: the Gini concentration index. Matrices in R. Examples. Example of matrix multiplication.  Arrays. Vectors, matrices, arrays: equivalence with mathematical objects. Examples with vectors and matrices.  Implementing set operations on sets represented as vectors: subset test, unique, union, intersection, difference. </v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>46086</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>14</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v>Lab 3 - Count inversions, Count values between, Max increment position</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
             <v>46090</v>
           </cell>
-          <cell r="B14" t="str">
+          <cell r="B16" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D16" t="str">
             <v xml:space="preserve">Gini Concentration Index.
 Data frames and motivations for their usage. Creating and using data frames. Input from file and data frame creation. Scan and read.csv. </v>
           </cell>
         </row>
-        <row r="15">
-          <cell r="A15">
-            <v>46091</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>Accessing and reshaping a data frame.</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>46092</v>
-          </cell>
-          <cell r="B16" t="str">
-            <v>Review of first part</v>
-          </cell>
-        </row>
         <row r="17">
           <cell r="A17">
-            <v>46100</v>
+            <v>46091</v>
           </cell>
           <cell r="B17" t="str">
-            <v>Lab 5 - Counting frequencies of modalities from csv</v>
+            <v>11</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D17" t="str">
+            <v>Accessing and reshaping a data frame.</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18">
+            <v>46092</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v>Review of first part</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>46093</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>14</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D19" t="str">
+            <v>Lab 4 - Polynomial in x, using power, Polynomial in x using Horner</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>46100</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v>Lab 5 - Counting frequencies of modalities from csv</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
             <v>46125</v>
           </cell>
-          <cell r="B18" t="str">
+          <cell r="B21" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D21" t="str">
             <v xml:space="preserve">Algorithms: sort. From algorithm to the R program. The bubble sort algorithm. 
 Recursive functions. Recursive vs iterative. Examples: Factorial, Fibonacci, Merge_Sort implementation and intuition on computational complexity. </v>
           </cell>
         </row>
-        <row r="19">
-          <cell r="A19">
-            <v>46126</v>
-          </cell>
-          <cell r="B19" t="str">
-            <v>Determinant of square matrix with Laplace formula. Examples with the matrix algebra. The echelon form: checking the condition. The elementary row operations. Echelon reduction</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>46127</v>
-          </cell>
-          <cell r="B20" t="str">
-            <v xml:space="preserve">Computing the determinant of a square matrix: the Laplace formula vs the echelon reduction: intuition on comparison of the computational complexities. </v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>46132</v>
-          </cell>
-          <cell r="B21" t="str">
-            <v xml:space="preserve">Introduction to computational complexity. Comparing the effort of different procedures that obtain the same result. Time complexity. Evaluation and comparison of complexities; asymptotic complexity. </v>
-          </cell>
-        </row>
         <row r="22">
           <cell r="A22">
-            <v>46133</v>
+            <v>46126</v>
           </cell>
           <cell r="B22" t="str">
-            <v>The "big O" notation. Comparing linear search and binary search. Examples of general algorithms and their computational complexity. The knapsack problem.</v>
+            <v>11</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v>Determinant of square matrix with Laplace formula. Examples with the matrix algebra. The echelon form: checking the condition. The elementary row operations. Echelon reduction</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23">
-            <v>46134</v>
+            <v>46127</v>
           </cell>
           <cell r="B23" t="str">
-            <v xml:space="preserve">Searching a sorted list: the binary search. Binary search. String manipulation with R. Example of summarisation of a data frame according to a categorical column. </v>
+            <v>11</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v xml:space="preserve">Computing the determinant of a square matrix: the Laplace formula vs the echelon reduction: intuition on comparison of the computational complexities. </v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24">
-            <v>46139</v>
+            <v>46128</v>
           </cell>
           <cell r="B24" t="str">
-            <v xml:space="preserve">Vectorization in R: implicit vectorization and vectorized functions. Comparisons of efficiency. The apply family of functions for the intrinsic vectorization. Subsetting data structures in R. Types of subsetting. Types of indexing. </v>
+            <v>11</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D24" t="str">
+            <v>Lab 6 - Quantiles from data frame read from csv</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25">
+            <v>46132</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v xml:space="preserve">Introduction to computational complexity. Comparing the effort of different procedures that obtain the same result. Time complexity. Evaluation and comparison of complexities; asymptotic complexity. </v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>46133</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D26" t="str">
+            <v>The "big O" notation. Comparing linear search and binary search. Examples of general algorithms and their computational complexity. The knapsack problem.</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>46134</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D27" t="str">
+            <v xml:space="preserve">Searching a sorted list: the binary search. Binary search. String manipulation with R. Example of summarisation of a data frame according to a categorical column. </v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>46135</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v>Lab 7 - Rectangles membership</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>46139</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v xml:space="preserve">Vectorization in R: implicit vectorization and vectorized functions. Comparisons of efficiency. The apply family of functions for the intrinsic vectorization. Subsetting data structures in R. Types of subsetting. Types of indexing. </v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
             <v>46140</v>
           </cell>
-          <cell r="B25" t="str">
+          <cell r="B30" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D30" t="str">
             <v xml:space="preserve">Strings and string functions. Regular expressions for string manipulation.
 Plotting data.  </v>
           </cell>
         </row>
-        <row r="26">
-          <cell r="A26">
-            <v>46141</v>
-          </cell>
-          <cell r="B26" t="str">
-            <v xml:space="preserve">The Lehmer generator. Generation of random numbers in R. Repetition of a random sequence by means of the seed. Types of generation: continuous uniform, discrete uniform, discrete with assigned probability. </v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>46146</v>
-          </cell>
-          <cell r="B27" t="str">
-            <v xml:space="preserve">Montecarlo methods. Computing Pi with Montecarlo method. Numerical methods. Minimum of a function with the golden section. Zeroes of a function with the Newton method. Zeroes of a function with the bisection method. </v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>46147</v>
-          </cell>
-          <cell r="B28" t="str">
-            <v>Numerical methods - continued</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>46148</v>
-          </cell>
-          <cell r="B29" t="str">
-            <v>Longitudinal data https://www.statmethods.net/input/dates.html</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>46153</v>
-          </cell>
-          <cell r="B30" t="str">
-            <v>Exercises on writing algorithms and translating algorithms to R: sequence analysis 1. Exercises on writing algorithms and translating algorithms to R: sequence analysis 3</v>
-          </cell>
-        </row>
         <row r="31">
           <cell r="A31">
-            <v>46154</v>
+            <v>46141</v>
           </cell>
           <cell r="B31" t="str">
-            <v>Exercises on writing algorithms and translating algorithms to R: sequence analysis 1. Exercises on writing algorithms and translating algorithms to R: sequence analysis 3</v>
+            <v>11</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D31" t="str">
+            <v xml:space="preserve">The Lehmer generator. Generation of random numbers in R. Repetition of a random sequence by means of the seed. Types of generation: continuous uniform, discrete uniform, discrete with assigned probability. </v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32">
+            <v>46142</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D32" t="str">
+            <v>Lab 8 - Analysis of string lenghts</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>46146</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C33" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D33" t="str">
+            <v xml:space="preserve">Montecarlo methods. Computing Pi with Montecarlo method. Numerical methods. Minimum of a function with the golden section. Zeroes of a function with the Newton method. Zeroes of a function with the bisection method. </v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>46147</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="C34" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D34" t="str">
+            <v>Numerical methods - continued</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>46148</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C35" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D35" t="str">
+            <v>Longitudinal data https://www.statmethods.net/input/dates.html</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>46149</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C36" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D36" t="str">
+            <v>Lab 9 - Classification of numeric values in ranges</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>46153</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C37" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D37" t="str">
+            <v>Exercises on writing algorithms and translating algorithms to R: sequence analysis 1. Exercises on writing algorithms and translating algorithms to R: sequence analysis 3</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>46154</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="C38" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D38" t="str">
+            <v>Exercises on writing algorithms and translating algorithms to R: sequence analysis 1. Exercises on writing algorithms and translating algorithms to R: sequence analysis 3</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
             <v>46155</v>
           </cell>
-          <cell r="B32" t="str">
+          <cell r="B39" t="str">
+            <v>9</v>
+          </cell>
+          <cell r="C39" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D39" t="str">
             <v>Exercises on writing algorithms and translating algorithms to R: sequence analysis 1. Exercises on writing algorithms and translating algorithms to R: sequence analysis 3</v>
           </cell>
         </row>
+        <row r="40">
+          <cell r="A40">
+            <v>46156</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>11</v>
+          </cell>
+          <cell r="C40" t="str">
+            <v>00</v>
+          </cell>
+          <cell r="D40" t="str">
+            <v>Lab 10 - Mock lab exam</v>
+          </cell>
+        </row>
       </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>3</v>
+    <v>8</v>
+    <v>39</v>
+    <v>6</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="colOffset" t="i"/>
+    <k n="errorType" t="i"/>
+    <k n="rwOffset" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -692,345 +1317,610 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F640DB1-D1BA-604D-B1C7-6E7D4447D468}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="130.83203125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" customWidth="1"/>
+    <col min="4" max="4" width="154.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="str">
-        <f>[1]Foglio2!A1</f>
-        <v>Date</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <f>[1]Foglio2!B1</f>
-        <v>Topics</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <f>[1]Foglio2!A2</f>
+    <row r="1" spans="1:4" ht="22" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A1" ca="1">[1]Foglio1!$A$1:$D$40</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A2" s="12">
         <v>46062</v>
       </c>
-      <c r="B2" s="3" t="str">
-        <f>[1]Foglio2!B2</f>
-        <v xml:space="preserve">General description of the course, assessment method. 
-Defining IT, a short history.
-Networking: lan, wan, network types, dns, url. </v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="68" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <f>[1]Foglio2!A3</f>
+      <c r="B2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <f>A2+1</f>
         <v>46063</v>
       </c>
-      <c r="B3" s="3" t="str">
-        <f>[1]Foglio2!B3</f>
-        <v xml:space="preserve">Computer Operation principles. Software and software layers. Instruction execution engine: the fetch/execute cycle and the clock. Architecture of a computer: the Von Neuman model. 
-Memories. Input/output devices. CPU types.
-Operating system. Bootstrap process. Multitasking. </v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <f>[1]Foglio2!A4</f>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <f>A3+1</f>
         <v>46064</v>
       </c>
-      <c r="B4" s="3" t="str">
-        <f>[1]Foglio2!B4</f>
-        <v xml:space="preserve">Digital representation of information. Numbers, characters. Integer and non-integer numbers: the binary representation; the mantissa/exponent representation and the floating point. Differences between real numbers and floating point: precision and approximation, arithmetic properties. </v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <f>[1]Foglio2!A5</f>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="84" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <f>A2+7</f>
         <v>46069</v>
       </c>
-      <c r="B5" s="3" t="str">
-        <f>[1]Foglio2!B5</f>
-        <v>Algorithmic thinking: the five properties of an algorithm. Programming languages and life cycle of a program. Examples of algorithms: the example of compound interest.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <f>[1]Foglio2!A6</f>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <f t="shared" ref="A6:A10" si="0">A3+7</f>
         <v>46070</v>
       </c>
-      <c r="B6" s="3" t="str">
-        <f>[1]Foglio2!B6</f>
-        <v>Writing loops. For and while constructs. 
-Compound interest in R. Integer division in R</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="85" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <f>[1]Foglio2!A7</f>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="147" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <f t="shared" si="0"/>
         <v>46071</v>
       </c>
-      <c r="B7" s="3" t="str">
-        <f>[1]Foglio2!B7</f>
-        <v xml:space="preserve">The Interactive Development Environment RStudio. Creating, editing and running an R program. Usage of the working windows, help system. Examples. 
-R - interactive and batch usage. The R  System Environment and the memory. Expressions and assignments. Operand Types. Operator types and priorities. Examples of expressions.
-Logical operators and De Morgan laws.
-Changing the type of an expression. Console input and output. Input from file. </v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <f>[1]Foglio2!A8</f>
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <f t="shared" si="0"/>
         <v>46076</v>
       </c>
-      <c r="B8" s="3" t="str">
-        <f>[1]Foglio2!B8</f>
-        <v xml:space="preserve">Repetition with for, sequences. Translation of the example of the compound interest into an R program. Discussion on the valid input ranges. Repetition based on condition. </v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <f>[1]Foglio2!A9</f>
+      <c r="B8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <f t="shared" si="0"/>
         <v>46077</v>
       </c>
-      <c r="B9" s="3" t="str">
-        <f>[1]Foglio2!B9</f>
-        <v xml:space="preserve">Example of exponential with McLaurin Formula. Conditional instructions. Nested conditional instructions, usage of braces. Sequences of instructions and blocks. Programming repetitions with the repeat construct. </v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <f>[1]Foglio2!A10</f>
+      <c r="B9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <f t="shared" si="0"/>
         <v>46078</v>
       </c>
-      <c r="B10" s="3" t="str">
-        <f>[1]Foglio2!B10</f>
-        <v>Examples of translation of algorithms in R: the computation of the exponential with the MacLaurin series. Conditional execution: the if construct. Chain of conditionals. From algorithm to R program</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <f>[1]Foglio2!A11</f>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>46079</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <f>A8+7</f>
         <v>46083</v>
       </c>
-      <c r="B11" s="3" t="str">
-        <f>[1]Foglio2!B11</f>
-        <v xml:space="preserve">Vectors and computations with vectors. Storing values in vectors, using values of vector elements. Looking for a value in a vector. More on vector index expression, selection of vector elements based on condition. </v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <f>[1]Foglio2!A12</f>
+      <c r="B12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <f>A9+7</f>
         <v>46084</v>
       </c>
-      <c r="B12" s="3" t="str">
-        <f>[1]Foglio2!B12</f>
-        <v xml:space="preserve">Abstractions and functions. Function version of the MacLaurin example. </v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <f>[1]Foglio2!A13</f>
+      <c r="B13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="84" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <f>A10+7</f>
         <v>46085</v>
       </c>
-      <c r="B13" s="3" t="str">
-        <f>[1]Foglio2!B13</f>
-        <v xml:space="preserve">Lists: creation and usage. Example of function returning a list. Exercise: the Gini concentration index. Matrices in R. Examples. Example of matrix multiplication.  Arrays. Vectors, matrices, arrays: equivalence with mathematical objects. Examples with vectors and matrices.  Implementing set operations on sets represented as vectors: subset test, unique, union, intersection, difference. </v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <f>[1]Foglio2!A14</f>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>46086</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="63" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <f>A12+7</f>
         <v>46090</v>
       </c>
-      <c r="B14" s="3" t="str">
-        <f>[1]Foglio2!B14</f>
-        <v xml:space="preserve">Gini Concentration Index.
-Data frames and motivations for their usage. Creating and using data frames. Input from file and data frame creation. Scan and read.csv. </v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <f>[1]Foglio2!A15</f>
+      <c r="B16" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <f>A13+7</f>
         <v>46091</v>
       </c>
-      <c r="B15" s="3" t="str">
-        <f>[1]Foglio2!B15</f>
-        <v>Accessing and reshaping a data frame.</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <f>[1]Foglio2!A16</f>
+      <c r="B17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <f>A14+7</f>
         <v>46092</v>
       </c>
-      <c r="B16" s="3" t="str">
-        <f>[1]Foglio2!B16</f>
-        <v>Review of first part</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <f>[1]Foglio2!A17</f>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>46093</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
         <v>46100</v>
       </c>
-      <c r="B17" s="3" t="str">
-        <f>[1]Foglio2!B17</f>
-        <v>Lab 5 - Counting frequencies of modalities from csv</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <f>[1]Foglio2!A18</f>
+      <c r="B20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="63" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
         <v>46125</v>
       </c>
-      <c r="B18" s="3" t="str">
-        <f>[1]Foglio2!B18</f>
-        <v xml:space="preserve">Algorithms: sort. From algorithm to the R program. The bubble sort algorithm. 
-Recursive functions. Recursive vs iterative. Examples: Factorial, Fibonacci, Merge_Sort implementation and intuition on computational complexity. </v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <f>[1]Foglio2!A19</f>
+      <c r="B21" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <f>A21+1</f>
         <v>46126</v>
       </c>
-      <c r="B19" s="3" t="str">
-        <f>[1]Foglio2!B19</f>
-        <v>Determinant of square matrix with Laplace formula. Examples with the matrix algebra. The echelon form: checking the condition. The elementary row operations. Echelon reduction</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <f>[1]Foglio2!A20</f>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <f>A22+1</f>
         <v>46127</v>
       </c>
-      <c r="B20" s="3" t="str">
-        <f>[1]Foglio2!B20</f>
-        <v xml:space="preserve">Computing the determinant of a square matrix: the Laplace formula vs the echelon reduction: intuition on comparison of the computational complexities. </v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <f>[1]Foglio2!A21</f>
+      <c r="B23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>46128</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <f>A21+7</f>
         <v>46132</v>
       </c>
-      <c r="B21" s="3" t="str">
-        <f>[1]Foglio2!B21</f>
-        <v xml:space="preserve">Introduction to computational complexity. Comparing the effort of different procedures that obtain the same result. Time complexity. Evaluation and comparison of complexities; asymptotic complexity. </v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <f>[1]Foglio2!A22</f>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
+        <f>A22+7</f>
         <v>46133</v>
       </c>
-      <c r="B22" s="3" t="str">
-        <f>[1]Foglio2!B22</f>
-        <v>The "big O" notation. Comparing linear search and binary search. Examples of general algorithms and their computational complexity. The knapsack problem.</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <f>[1]Foglio2!A23</f>
+      <c r="B26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
+        <f>A23+7</f>
         <v>46134</v>
       </c>
-      <c r="B23" s="3" t="str">
-        <f>[1]Foglio2!B23</f>
-        <v xml:space="preserve">Searching a sorted list: the binary search. Binary search. String manipulation with R. Example of summarisation of a data frame according to a categorical column. </v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <f>[1]Foglio2!A24</f>
+      <c r="B27" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <v>46135</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <f>A25+7</f>
         <v>46139</v>
       </c>
-      <c r="B24" s="3" t="str">
-        <f>[1]Foglio2!B24</f>
-        <v xml:space="preserve">Vectorization in R: implicit vectorization and vectorized functions. Comparisons of efficiency. The apply family of functions for the intrinsic vectorization. Subsetting data structures in R. Types of subsetting. Types of indexing. </v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <f>[1]Foglio2!A25</f>
+      <c r="B29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <f>A26+7</f>
         <v>46140</v>
       </c>
-      <c r="B25" s="3" t="str">
-        <f>[1]Foglio2!B25</f>
-        <v xml:space="preserve">Strings and string functions. Regular expressions for string manipulation.
-Plotting data.  </v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <f>[1]Foglio2!A26</f>
+      <c r="B30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <f>A27+7</f>
         <v>46141</v>
       </c>
-      <c r="B26" s="3" t="str">
-        <f>[1]Foglio2!B26</f>
-        <v xml:space="preserve">The Lehmer generator. Generation of random numbers in R. Repetition of a random sequence by means of the seed. Types of generation: continuous uniform, discrete uniform, discrete with assigned probability. </v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <f>[1]Foglio2!A27</f>
+      <c r="B31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <v>46142</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <f>A29+7</f>
         <v>46146</v>
       </c>
-      <c r="B27" s="3" t="str">
-        <f>[1]Foglio2!B27</f>
-        <v xml:space="preserve">Montecarlo methods. Computing Pi with Montecarlo method. Numerical methods. Minimum of a function with the golden section. Zeroes of a function with the Newton method. Zeroes of a function with the bisection method. </v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <f>[1]Foglio2!A28</f>
+      <c r="B33" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <f>A30+7</f>
         <v>46147</v>
       </c>
-      <c r="B28" s="3" t="str">
-        <f>[1]Foglio2!B28</f>
-        <v>Numerical methods - continued</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <f>[1]Foglio2!A29</f>
+      <c r="B34" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <f>A31+7</f>
         <v>46148</v>
       </c>
-      <c r="B29" s="3" t="str">
-        <f>[1]Foglio2!B29</f>
-        <v>Longitudinal data https://www.statmethods.net/input/dates.html</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <f>[1]Foglio2!A30</f>
+      <c r="B35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>46149</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <f>A33+7</f>
         <v>46153</v>
       </c>
-      <c r="B30" s="3" t="str">
-        <f>[1]Foglio2!B30</f>
-        <v>Exercises on writing algorithms and translating algorithms to R: sequence analysis 1. Exercises on writing algorithms and translating algorithms to R: sequence analysis 3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
-        <f>[1]Foglio2!A31</f>
+      <c r="B37" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <f>A34+7</f>
         <v>46154</v>
       </c>
-      <c r="B31" s="3" t="str">
-        <f>[1]Foglio2!B31</f>
-        <v>Exercises on writing algorithms and translating algorithms to R: sequence analysis 1. Exercises on writing algorithms and translating algorithms to R: sequence analysis 3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
-        <f>[1]Foglio2!A32</f>
+      <c r="B38" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <f>A35+7</f>
         <v>46155</v>
       </c>
-      <c r="B32" s="3" t="str">
-        <f>[1]Foglio2!B32</f>
-        <v>Exercises on writing algorithms and translating algorithms to R: sequence analysis 1. Exercises on writing algorithms and translating algorithms to R: sequence analysis 3</v>
+      <c r="B39" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A40" s="8">
+        <v>46156</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Errore" error="Seleziona una delle voci dall'elenco" promptTitle="Compilazione" prompt="Seleziona una delle voci valide cliccando la freccia sulla destra" sqref="C2:C40" xr:uid="{613BE364-C2E1-8B4A-92ED-1793B34E447C}">
+      <formula1>"00,15,30,45"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Errore" error="Seleziona una delle voci dall'elenco" promptTitle="Compilazione" prompt="Seleziona una delle voci valide cliccando la freccia sulla destra" sqref="B2:B40" xr:uid="{C05B7788-E0CA-CA48-9521-CB73F516598C}">
+      <formula1>"7,8,9,10,11,12,13,14,15,16,17,18,19,20,21"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>